--- a/plantilla_control_herramientas.xlsx
+++ b/plantilla_control_herramientas.xlsx
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -472,10 +472,13 @@
       <c r="D1" t="str">
         <v>telefono</v>
       </c>
+      <c r="E1" t="str">
+        <v>contrasena</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/plantilla_control_herramientas.xlsx
+++ b/plantilla_control_herramientas.xlsx
@@ -457,7 +457,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:D1"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -472,13 +472,10 @@
       <c r="D1" t="str">
         <v>telefono</v>
       </c>
-      <c r="E1" t="str">
-        <v>contrasena</v>
-      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D1"/>
   </ignoredErrors>
 </worksheet>
 </file>
